--- a/branches/pt/ValueSet-dose-form-ontology-cs.xlsx
+++ b/branches/pt/ValueSet-dose-form-ontology-cs.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EDQM-DOSEFORM-ONT-VS</t>
+    <t>EDQM_DOSEFORM_ONT_VS</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
